--- a/output/pdf_financials_xlsx/BP.H.xlsx
+++ b/output/pdf_financials_xlsx/BP.H.xlsx
@@ -1285,25 +1285,25 @@
         <v>-0.354232</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.08291900000000001</v>
+        <v>-0.08291900000000001</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.047609</v>
+        <v>-0.047609</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.062408</v>
+        <v>-0.062408</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.349358</v>
+        <v>-0.349358</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-1.191509</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.191509</v>
+        <v>-1.191509</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.07216599999999999</v>
+        <v>-0.07216599999999999</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-0.195405</v>
@@ -1337,7 +1337,7 @@
         <v>0.045134</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.708464</v>
+        <v>-0</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -1566,28 +1566,28 @@
         <v>-1.196344</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.354232</v>
+        <v>-0.354232</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.08291900000000001</v>
+        <v>-0.08291900000000001</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.047609</v>
+        <v>-0.047609</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.062408</v>
+        <v>-0.062408</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.349358</v>
+        <v>-0.349358</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-1.191509</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.191509</v>
+        <v>-1.191509</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.07216599999999999</v>
+        <v>-0.07216599999999999</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.195405</v>
@@ -1731,28 +1731,28 @@
         <v>-1.196344</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.354232</v>
+        <v>-0.354232</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.08291900000000001</v>
+        <v>-0.08291900000000001</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.047609</v>
+        <v>-0.047609</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.062408</v>
+        <v>-0.062408</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.349358</v>
+        <v>-0.349358</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-1.191509</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.191509</v>
+        <v>-1.191509</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.07216599999999999</v>
+        <v>-0.07216599999999999</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-0.195405</v>
@@ -1954,25 +1954,25 @@
         <v>-0.354232</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.08291900000000001</v>
+        <v>-0.08291900000000001</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.047609</v>
+        <v>-0.047609</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.062408</v>
+        <v>-0.062408</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.349358</v>
+        <v>-0.349358</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-1.191509</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.191509</v>
+        <v>-1.191509</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.07216599999999999</v>
+        <v>-0.07216599999999999</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-0.195405</v>
@@ -2064,25 +2064,25 @@
         <v>-0.354232</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.08291900000000001</v>
+        <v>-0.08291900000000001</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.047609</v>
+        <v>-0.047609</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.062408</v>
+        <v>-0.062408</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.349358</v>
+        <v>-0.349358</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-1.191509</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.191509</v>
+        <v>-1.191509</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.07216599999999999</v>
+        <v>-0.07216599999999999</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-0.195405</v>
@@ -2197,28 +2197,28 @@
         <v>-3.635505421763415</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-200</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-0</v>
@@ -6296,16 +6296,16 @@
         <v>0</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>0</v>
+        <v>0.003226</v>
       </c>
       <c r="O103" s="3" t="n">
-        <v>0</v>
+        <v>-4.3e-05</v>
       </c>
       <c r="P103" s="3" t="n">
-        <v>0</v>
+        <v>-0.001017</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>0</v>
+        <v>-0.007941</v>
       </c>
     </row>
     <row r="104">
@@ -8374,7 +8374,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>-</t>
@@ -21144,7 +21148,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -44590,13 +44598,13 @@
         </is>
       </c>
       <c r="M384" s="5" t="n">
-        <v>0.441751</v>
+        <v>-0.441751</v>
       </c>
       <c r="N384" s="5" t="n">
-        <v>1.191509</v>
+        <v>-1.191509</v>
       </c>
       <c r="O384" s="5" t="n">
-        <v>0.07216599999999999</v>
+        <v>-0.07216599999999999</v>
       </c>
       <c r="P384" t="inlineStr">
         <is>
@@ -46653,10 +46661,10 @@
         </is>
       </c>
       <c r="H406" s="5" t="n">
-        <v>0.354232</v>
+        <v>-0.354232</v>
       </c>
       <c r="I406" s="5" t="n">
-        <v>0.08291900000000001</v>
+        <v>-0.08291900000000001</v>
       </c>
       <c r="J406" t="inlineStr">
         <is>
@@ -46669,10 +46677,10 @@
         </is>
       </c>
       <c r="L406" s="5" t="n">
-        <v>0.349358</v>
+        <v>-0.349358</v>
       </c>
       <c r="M406" s="5" t="n">
-        <v>0.441751</v>
+        <v>-0.441751</v>
       </c>
       <c r="N406" t="inlineStr">
         <is>
@@ -47128,13 +47136,13 @@
         </is>
       </c>
       <c r="I411" s="5" t="n">
-        <v>0.08291900000000001</v>
+        <v>-0.08291900000000001</v>
       </c>
       <c r="J411" s="5" t="n">
-        <v>0.047609</v>
+        <v>-0.047609</v>
       </c>
       <c r="K411" s="5" t="n">
-        <v>0.062408</v>
+        <v>-0.062408</v>
       </c>
       <c r="L411" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BP.H.xlsx
+++ b/output/pdf_financials_xlsx/BP.H.xlsx
@@ -953,28 +953,28 @@
         <v>0.021567</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.060308</v>
+        <v>0.44432</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.109383</v>
+        <v>0.741926</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.013565</v>
+        <v>0.090672</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.011895</v>
+        <v>0.195394</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.040953</v>
+        <v>0.392992</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.004519</v>
+        <v>0.079254</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.028557</v>
+        <v>0.110881</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.026298</v>
+        <v>0.269161</v>
       </c>
     </row>
     <row r="11">
@@ -1062,19 +1062,19 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000424</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002577</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000833</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000472</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000163</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1951,19 +1951,19 @@
         <v>-1.241478</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.354232</v>
+        <v>-0.354656</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.08291900000000001</v>
+        <v>-0.085496</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.047609</v>
+        <v>-0.048442</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.062408</v>
+        <v>-0.06288000000000001</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.349358</v>
+        <v>-0.349521</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-1.191509</v>
@@ -2061,19 +2061,19 @@
         <v>-1.213758</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.354232</v>
+        <v>-0.354656</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.08291900000000001</v>
+        <v>-0.085496</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.047609</v>
+        <v>-0.048442</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.062408</v>
+        <v>-0.06288000000000001</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.349358</v>
+        <v>-0.349521</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-1.191509</v>
@@ -2331,13 +2331,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.057345</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.000929</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.027926</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.260452</v>
@@ -2358,25 +2358,25 @@
         <v>0.61977</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.071905</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.047667</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.301448</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.081385</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.02795</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.189734</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.101435</v>
       </c>
     </row>
     <row r="35">
@@ -2441,13 +2441,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.057345</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.000929</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.027926</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.260452</v>
@@ -2468,25 +2468,25 @@
         <v>0.61977</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.071905</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.047667</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.301448</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.081385</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.02795</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.189734</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.101435</v>
       </c>
     </row>
     <row r="37">
@@ -3101,13 +3101,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.165543</v>
+        <v>2.108198</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.958057</v>
+        <v>0.957128</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.320917</v>
+        <v>0.292991</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -3128,25 +3128,25 @@
         <v>0.08837100000000001</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.11838</v>
+        <v>0.046475</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.054986</v>
+        <v>0.007319</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.47682</v>
+        <v>0.175372</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.08353099999999999</v>
+        <v>0.002146</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.030139</v>
+        <v>0.002189</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.19294</v>
+        <v>0.003206</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.112582</v>
+        <v>0.011147</v>
       </c>
     </row>
     <row r="49">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
@@ -38828,7 +38828,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -42362,7 +42362,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -46550,7 +46550,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -47780,7 +47780,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">

--- a/output/pdf_financials_xlsx/BP.H.xlsx
+++ b/output/pdf_financials_xlsx/BP.H.xlsx
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.094626</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.003465</v>
+        <v>0.099301</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.02772</v>
+        <v>0.07062400000000001</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0</v>
@@ -2052,13 +2052,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.287883</v>
+        <v>-2.193257</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.408088</v>
+        <v>-2.312252</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.213758</v>
+        <v>-1.170854</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.354656</v>
@@ -2107,13 +2107,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-68.20955954584659</v>
+        <v>-65.38843723251794</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-82.63057590171439</v>
+        <v>-79.34208151441761</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-48.06939531376484</v>
+        <v>-46.37023507215015</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -6095,13 +6095,13 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.094899</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.099301</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.07062400000000001</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0</v>
@@ -29354,7 +29354,11 @@
           <t>Amortization of tangible assets</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -29452,7 +29456,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -33010,7 +33014,11 @@
           <t>Amortization of tangible assets</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E261" s="5" t="n">
         <v>0.094899</v>
       </c>
@@ -33104,7 +33112,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -50264,7 +50272,11 @@
           <t>Amortization of tangible assets</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E444" t="inlineStr">
         <is>
           <t>-</t>
@@ -50362,7 +50374,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -52558,7 +52570,11 @@
           <t>Amortization of tangible assets</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E468" s="5" t="n">
         <v>0.094626</v>
       </c>
@@ -52652,7 +52668,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">

--- a/output/pdf_financials_xlsx/BP.H.xlsx
+++ b/output/pdf_financials_xlsx/BP.H.xlsx
@@ -6162,7 +6162,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001537</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>0</v>
@@ -6700,13 +6700,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.128733</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.056868</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001001</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -6978,10 +6978,10 @@
         <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.187112</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>0.01275</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-0.203745</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -8033,13 +8033,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.128733</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.056868</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001001</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -8088,13 +8088,13 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.976536</v>
+        <v>-2.105269</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.312135</v>
+        <v>-0.369003</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.628161</v>
+        <v>-0.629162</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-0.277145</v>
@@ -27616,7 +27616,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -30896,7 +30900,11 @@
           <t>to purchases of equipment</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -31862,7 +31870,11 @@
           <t>Issuance of shares for acquisition of intangible assets $</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -34550,7 +34562,11 @@
           <t>Cash used for purchases of equipment</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E277" s="5" t="n">
         <v>-0.128733</v>
       </c>
@@ -34642,7 +34658,11 @@
           <t>(Decrease) in accounts payable and accrued liabilities relating to purchases of equipment</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -34832,7 +34852,11 @@
           <t>Cash used for purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -34928,7 +34952,11 @@
           <t>Increase in short-term debt relating to purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -35024,7 +35052,11 @@
           <t>Increase in liability to be settled by the issuance of shares relating to purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -36364,7 +36396,11 @@
           <t>Issuance of shares for acquisition of intangible assets (Note 6) $</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -37032,7 +37068,11 @@
           <t>Increase in accounts payable and accrued liabilities relating to purchases of equipment</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E303" s="5" t="n">
         <v>0.00323</v>
       </c>
@@ -37126,7 +37166,11 @@
           <t>Cash used for purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -37320,7 +37364,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E306" s="5" t="n">
         <v>-0.203745</v>
       </c>
